--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-DiagnosticResults-ips.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-DiagnosticResults-ips.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T14:21:24+00:00</t>
+    <t>2025-01-13T17:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
